--- a/artfynd/A 8065-2025 artfynd.xlsx
+++ b/artfynd/A 8065-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125024052</v>
       </c>
       <c r="B2" t="n">
-        <v>110729</v>
+        <v>110732</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 8065-2025 artfynd.xlsx
+++ b/artfynd/A 8065-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125024052</v>
       </c>
       <c r="B2" t="n">
-        <v>110732</v>
+        <v>110819</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 8065-2025 artfynd.xlsx
+++ b/artfynd/A 8065-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125024052</v>
       </c>
       <c r="B2" t="n">
-        <v>110819</v>
+        <v>110822</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 8065-2025 artfynd.xlsx
+++ b/artfynd/A 8065-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125024052</v>
       </c>
       <c r="B2" t="n">
-        <v>110822</v>
+        <v>110848</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 8065-2025 artfynd.xlsx
+++ b/artfynd/A 8065-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125024052</v>
       </c>
       <c r="B2" t="n">
-        <v>110848</v>
+        <v>110849</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 8065-2025 artfynd.xlsx
+++ b/artfynd/A 8065-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125024052</v>
       </c>
       <c r="B2" t="n">
-        <v>110849</v>
+        <v>110850</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 8065-2025 artfynd.xlsx
+++ b/artfynd/A 8065-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,27 +675,27 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125024052</v>
+        <v>124999983</v>
       </c>
       <c r="B2" t="n">
-        <v>110850</v>
+        <v>101897</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221049</v>
+        <v>220075</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Småvänderot</t>
+          <t>Gullpudra</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Valeriana dioica</t>
+          <t>Chrysosplenium alternifolium</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -703,29 +703,28 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Brammarp,1,1 km NV, Småvänderot, Sk</t>
+          <t>Brammarp 1100m NV, Sk</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>372501</v>
+        <v>372483</v>
       </c>
       <c r="R2" t="n">
-        <v>6248645</v>
+        <v>6248677</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -747,11 +746,6 @@
           <t>Hjärnarp</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>M-Äng-0218</t>
-        </is>
-      </c>
       <c r="Y2" t="inlineStr">
         <is>
           <t>2025-04-30</t>
@@ -760,11 +754,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-04-30</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>18 ex i knopp inom 10m</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -773,18 +762,19 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>Bäck öster om E6</t>
+          <t>bäckkant</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Charlotte Wigermo</t>
+          <t>Joachim Falck</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
@@ -792,23 +782,14 @@
           <t>Joachim Falck</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
+      <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
         <v>81390415</v>
       </c>
       <c r="B3" t="n">
-        <v>106964</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>110078</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -840,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>372476.5763448753</v>
+        <v>372477</v>
       </c>
       <c r="R3" t="n">
-        <v>6248653.039502296</v>
+        <v>6248653</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -873,19 +854,9 @@
           <t>2013-06-11</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2013-06-11</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -916,6 +887,131 @@
       <c r="AY3" t="inlineStr">
         <is>
           <t>Skånes Flora Millora 2008-2015</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>125024052</v>
+      </c>
+      <c r="B4" t="n">
+        <v>111128</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>221049</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Småvänderot</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Valeriana dioica</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Brammarp,1,1 km NV, Småvänderot, Sk</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>372501</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6248645</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Ängelholm</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Hjärnarp</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>M-Äng-0218</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-04-30</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-04-30</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>18 ex i knopp inom 10m</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>Bäck öster om E6</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Charlotte Wigermo</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Joachim Falck</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
         </is>
       </c>
     </row>

--- a/artfynd/A 8065-2025 artfynd.xlsx
+++ b/artfynd/A 8065-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -783,6 +788,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124999983</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -889,6 +899,11 @@
           <t>Skånes Flora Millora 2008-2015</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/81390415</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1014,8 +1029,18 @@
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125024052</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>